--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电一页纸_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电一页纸_v4.3.xlsx
@@ -10,7 +10,7 @@
     <sheet name="一页纸" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'一页纸'!$A$1:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'一页纸'!$A$1:$I$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>305.1412</v>
+        <v>125.3388784020734</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>6103.2921</v>
+        <v>6103.292119896927</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>16614.6329</v>
+        <v>21970.52218391663</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1570.4536</v>
+        <v>1004.108720496838</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>5496.6412</v>
+        <v>5496.641223759201</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>13461.3107</v>
+        <v>18468.68812147818</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>-1265.3124</v>
+        <v>-878.7698420947646</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>606.6509</v>
+        <v>606.6508961377258</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>3153.3222</v>
+        <v>3501.834062438452</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -629,13 +629,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.0153</v>
+        <v>0.006266943920103671</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.3052</v>
+        <v>0.3051646059948463</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.8307</v>
+        <v>1.098526109195832</v>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
@@ -666,13 +666,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>363.9811</v>
+        <v>309.1060776686348</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>850.4145</v>
+        <v>850.4145244059906</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1648.2722</v>
+        <v>1827.193894240415</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.9204</v>
+        <v>0.7816414801061013</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1.141</v>
+        <v>1.141021711514065</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1.3221</v>
+        <v>1.465610163503797</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -748,13 +748,13 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>5.8528</v>
+        <v>6.004223072264262</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>5.6711</v>
+        <v>5.671135378218963</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>5.5736</v>
+        <v>5.517439884994116</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -789,13 +789,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2.2212</v>
+        <v>2.165142740957083</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>3.174</v>
+        <v>3.173967609578199</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>3.9472</v>
+        <v>3.987356538280337</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2287.6995</v>
+        <v>2287.699543794185</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4297.2917</v>
+        <v>4297.291663508309</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7179.0234</v>
+        <v>7179.023394504345</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>366.0319</v>
+        <v>343.1549315691277</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>687.5667</v>
+        <v>687.5666661613295</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1148.6437</v>
+        <v>897.3779243130431</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>343.1549</v>
+        <v>343.1549315691277</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>644.5937</v>
+        <v>644.5937495262464</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1076.8535</v>
+        <v>1076.853509175652</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -953,13 +953,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1570.4536</v>
+        <v>1004.108720496838</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>5496.6412</v>
+        <v>5496.641223759201</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>13461.3107</v>
+        <v>18468.68812147818</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -985,22 +985,22 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>其中多少是「押注」（倍数法 − DCF）？</t>
+          <t>同一门生意，改用 DCF 有限期账（15 年截断）算，CATL 归属多少？</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>押注部分（结构性差值）</t>
+          <t>CATL归属价值（DCF口径，有限期账/基础账，本轮新主口径）</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>714.7991</v>
+        <v>573.0345402621705</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>3472.7603</v>
+        <v>2023.880910498512</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>9476.3554</v>
+        <v>5247.366344163119</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1009,104 +1009,186 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>中性押注 3,473 亿 ÷ 归属 5,497 亿 ＝ **63%**，已在 50% 线之上、70% 线之下（灰区）。&lt;50% 可坦然辩护；&gt;70% 则结论主要靠倍数而非现金流。</t>
+          <t>与上一行倍数法并排看：DCF 是「现金流说了算」的口径，倍数法是「市场愿意给多少」的口径。两者差额就是押注（见下一行）。</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>押注 &gt;70% 时，结论主要建立在倍数判断而非现金流上。</t>
+          <t>若 DCF 口径远低于倍数法，说明拍的倍数含大量战略溢价——这正是 3.17× 那行的来处。</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>两口径自 2026-09-04 起共用同一稳态 debt（口径已统一，见 DECISIONS）</t>
+          <t>15 年分析期、WACC 7.5%；2030 年后不建模规模增长（capex诊断.md §8.4 既定假设）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>盘子有多大（电量口径）？</t>
+          <t>**标准达成后**：按 2030 年规模永续经营，CATL 归属多少（价值上限）？</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>年换电交易电量（成熟期）</t>
+          <t>CATL归属价值（DCF口径，永续账/开放上限）</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>788.573</v>
+        <v>443.7421403356877</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1450.3754</v>
+        <v>2088.73191426347</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>2360.7368</v>
+        <v>6084.888231394231</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>亿kWh</t>
+          <t>亿元</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>中性 1,450 亿 kWh/年。可拿全国电动车用电量做量级交叉校验。</t>
+          <t>应显著高于有限期账（不再截断）。**但要注意**：这是「规模冻结在 2030 年」的永续——模型不建模 2030 后增长，所以它是**模型内的上限、真实世界的下限**。若标准真跑通、规模继续扩张，真值会高于它。</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>若日换电次数（中性 329 万次/日）反推的换电车辆数超出保有量常识，则车辆口径虚高。</t>
+          <t>永续账靠「稳态净更新支出」与 g（电池价格长期降幅）支撑：更新支出若被低估、或 g 取太高，永续账会虚高。反过来——**若永续账都撑不起 18×，那倍数法就确实主要是押注**。</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>分母（商用保有量 900 万/1,500 万、NEV 渗透率）**待补中汽协/乘联会上险外部独立信源**</t>
+          <t>更新支出用 renewal theory（更新理论第一性原理）；g＝电池价格曲线长期降幅（均为模型内部推导，非外部信源）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>其中多少是「押注」（倍数法 − DCF）？</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>押注部分（结构性差值）</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>431.0741802346676</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>3472.760313260689</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>13221.32177731506</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>中性押注 3,473 亿 ÷ 归属 5,497 亿 ＝ **63%**，已在 50% 线之上、70% 线之下（灰区）。&lt;50% 可坦然辩护；&gt;70% 则结论主要靠倍数而非现金流。</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>押注 &gt;70% 时，结论主要建立在倍数判断而非现金流上。</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>两口径自 2026-09-04 起共用同一稳态 debt（口径已统一，见 DECISIONS）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>盘子有多大（电量口径）？</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>年换电交易电量（成熟期）</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>788.57296</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>1450.37536</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>2360.73684</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>亿kWh</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>中性 1,450 亿 kWh/年。可拿全国电动车用电量做量级交叉校验。</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>若日换电次数（中性 329 万次/日）反推的换电车辆数超出保有量常识，则车辆口径虚高。</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>分母（商用保有量 900 万/1,500 万、NEV 渗透率）**待补中汽协/乘联会上险外部独立信源**</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>要建多少站？</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>站数合计</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C18" s="3" t="n">
         <v>6919</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>11285</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>16661</v>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>座</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>中性 11,285 座；其中重卡站可对照政策口径做量级校验。</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>若单站日服务能力假设偏乐观，站数与 CAPEX 会被系统性低估。</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>重卡干线对照 52 号文 3,000 座（模型内已登记交叉验证）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I16"/>
+  <autoFilter ref="A1:I18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>